--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.980696727564859</v>
+        <v>0.8093632182292896</v>
       </c>
       <c r="D2" t="n">
-        <v>5.328384450321535</v>
+        <v>0.8658624731772494</v>
       </c>
       <c r="E2" t="n">
-        <v>10.74255484797119</v>
+        <v>1.745665162795319</v>
       </c>
       <c r="F2" t="n">
-        <v>10.60004742886713</v>
+        <v>1.722507707190909</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.71758972544099</v>
+        <v>2.22910833038416</v>
       </c>
       <c r="D3" t="n">
-        <v>13.95171663239661</v>
+        <v>2.267153952764449</v>
       </c>
       <c r="E3" t="n">
-        <v>10.74255484797119</v>
+        <v>1.745665162795319</v>
       </c>
       <c r="F3" t="n">
-        <v>10.60004742886713</v>
+        <v>1.722507707190909</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.59645593185186</v>
+        <v>3.021924088925927</v>
       </c>
       <c r="D4" t="n">
-        <v>18.06672931586769</v>
+        <v>2.9358435138285</v>
       </c>
       <c r="E4" t="n">
-        <v>10.74255484797119</v>
+        <v>1.745665162795319</v>
       </c>
       <c r="F4" t="n">
-        <v>10.60004742886713</v>
+        <v>1.722507707190909</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>2.379194690106203</v>
+        <v>0.386619137142258</v>
       </c>
       <c r="D5" t="n">
-        <v>2.622964515590692</v>
+        <v>0.4262317337834874</v>
       </c>
       <c r="E5" t="n">
-        <v>10.74255484797119</v>
+        <v>1.745665162795319</v>
       </c>
       <c r="F5" t="n">
-        <v>10.60004742886713</v>
+        <v>1.722507707190909</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.36242318083379</v>
+        <v>2.821393766885492</v>
       </c>
       <c r="D6" t="n">
-        <v>17.62191293813992</v>
+        <v>2.863560852447738</v>
       </c>
       <c r="E6" t="n">
-        <v>10.74255484797119</v>
+        <v>1.745665162795319</v>
       </c>
       <c r="F6" t="n">
-        <v>10.60004742886713</v>
+        <v>1.722507707190909</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.47902429404194</v>
+        <v>2.352841447781815</v>
       </c>
       <c r="D7" t="n">
-        <v>14.62166464054774</v>
+        <v>2.376020504089008</v>
       </c>
       <c r="E7" t="n">
-        <v>10.74255484797119</v>
+        <v>1.745665162795319</v>
       </c>
       <c r="F7" t="n">
-        <v>10.60004742886713</v>
+        <v>1.722507707190909</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.03637304028773</v>
+        <v>6.180910619046756</v>
       </c>
       <c r="D8" t="n">
-        <v>37.93605633270874</v>
+        <v>6.16460915406517</v>
       </c>
       <c r="E8" t="n">
-        <v>10.74255484797119</v>
+        <v>1.745665162795319</v>
       </c>
       <c r="F8" t="n">
-        <v>10.60004742886713</v>
+        <v>1.722507707190909</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
